--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N44_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N44_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>4.283122344732831</v>
+        <v>0.6960073810190851</v>
       </c>
       <c r="D2" t="n">
-        <v>1.283131555244582</v>
+        <v>0.2085088777272445</v>
       </c>
       <c r="E2" t="n">
-        <v>16.2050632490384</v>
+        <v>2.63332277796874</v>
       </c>
       <c r="F2" t="n">
-        <v>11.75278759208115</v>
+        <v>1.909827983713187</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.8716910332852</v>
+        <v>1.766649792908845</v>
       </c>
       <c r="D3" t="n">
-        <v>11.16945651255629</v>
+        <v>1.815036683290397</v>
       </c>
       <c r="E3" t="n">
-        <v>16.2050632490384</v>
+        <v>2.63332277796874</v>
       </c>
       <c r="F3" t="n">
-        <v>11.75278759208115</v>
+        <v>1.909827983713187</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>8.373747038843092</v>
+        <v>1.360733893812003</v>
       </c>
       <c r="D4" t="n">
-        <v>8.770667222164931</v>
+        <v>1.425233423601801</v>
       </c>
       <c r="E4" t="n">
-        <v>16.2050632490384</v>
+        <v>2.63332277796874</v>
       </c>
       <c r="F4" t="n">
-        <v>11.75278759208115</v>
+        <v>1.909827983713187</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>32.85215819869246</v>
+        <v>5.338475707287524</v>
       </c>
       <c r="D5" t="n">
-        <v>18.36368623531992</v>
+        <v>2.984099013239487</v>
       </c>
       <c r="E5" t="n">
-        <v>16.2050632490384</v>
+        <v>2.63332277796874</v>
       </c>
       <c r="F5" t="n">
-        <v>11.75278759208115</v>
+        <v>1.909827983713187</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>20.11218536111877</v>
+        <v>3.2682301211818</v>
       </c>
       <c r="D6" t="n">
-        <v>15.9417682985857</v>
+        <v>2.590537348520177</v>
       </c>
       <c r="E6" t="n">
-        <v>16.2050632490384</v>
+        <v>2.63332277796874</v>
       </c>
       <c r="F6" t="n">
-        <v>11.75278759208115</v>
+        <v>1.909827983713187</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>38.32694421431816</v>
+        <v>6.228128434826702</v>
       </c>
       <c r="D7" t="n">
-        <v>20.37566064428856</v>
+        <v>3.311044854696891</v>
       </c>
       <c r="E7" t="n">
-        <v>16.2050632490384</v>
+        <v>2.63332277796874</v>
       </c>
       <c r="F7" t="n">
-        <v>11.75278759208115</v>
+        <v>1.909827983713187</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>6.576473218982953</v>
+        <v>1.06867689808473</v>
       </c>
       <c r="D8" t="n">
-        <v>11.76543078895704</v>
+        <v>1.911882503205518</v>
       </c>
       <c r="E8" t="n">
-        <v>16.2050632490384</v>
+        <v>2.63332277796874</v>
       </c>
       <c r="F8" t="n">
-        <v>11.75278759208115</v>
+        <v>1.909827983713187</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>23.42572348674231</v>
+        <v>3.806680066595626</v>
       </c>
       <c r="D9" t="n">
-        <v>13.45127947568912</v>
+        <v>2.185832914799482</v>
       </c>
       <c r="E9" t="n">
-        <v>16.2050632490384</v>
+        <v>2.63332277796874</v>
       </c>
       <c r="F9" t="n">
-        <v>11.75278759208115</v>
+        <v>1.909827983713187</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>16.61861376674444</v>
+        <v>2.700524737095972</v>
       </c>
       <c r="D10" t="n">
-        <v>17.73324662329854</v>
+        <v>2.881652576286013</v>
       </c>
       <c r="E10" t="n">
-        <v>16.2050632490384</v>
+        <v>2.63332277796874</v>
       </c>
       <c r="F10" t="n">
-        <v>11.75278759208115</v>
+        <v>1.909827983713187</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>17.53976582976338</v>
+        <v>2.850211947336549</v>
       </c>
       <c r="D11" t="n">
-        <v>35.81249796890109</v>
+        <v>5.819530919946428</v>
       </c>
       <c r="E11" t="n">
-        <v>16.2050632490384</v>
+        <v>2.63332277796874</v>
       </c>
       <c r="F11" t="n">
-        <v>11.75278759208115</v>
+        <v>1.909827983713187</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>14.62839923680078</v>
+        <v>2.377114875980126</v>
       </c>
       <c r="D12" t="n">
-        <v>29.19121536422125</v>
+        <v>4.743572496685953</v>
       </c>
       <c r="E12" t="n">
-        <v>16.2050632490384</v>
+        <v>2.63332277796874</v>
       </c>
       <c r="F12" t="n">
-        <v>11.75278759208115</v>
+        <v>1.909827983713187</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>38.28543724080895</v>
+        <v>6.221383551631454</v>
       </c>
       <c r="D13" t="n">
-        <v>41.72285080218266</v>
+        <v>6.779963255354683</v>
       </c>
       <c r="E13" t="n">
-        <v>16.2050632490384</v>
+        <v>2.63332277796874</v>
       </c>
       <c r="F13" t="n">
-        <v>11.75278759208115</v>
+        <v>1.909827983713187</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>23.12230831848994</v>
+        <v>3.757375101754616</v>
       </c>
       <c r="D14" t="n">
-        <v>17.68243015937966</v>
+        <v>2.873394900899195</v>
       </c>
       <c r="E14" t="n">
-        <v>16.2050632490384</v>
+        <v>2.63332277796874</v>
       </c>
       <c r="F14" t="n">
-        <v>11.75278759208115</v>
+        <v>1.909827983713187</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>25.5627030894026</v>
+        <v>4.153939252027922</v>
       </c>
       <c r="D15" t="n">
-        <v>39.80730729855576</v>
+        <v>6.468687436015312</v>
       </c>
       <c r="E15" t="n">
-        <v>16.2050632490384</v>
+        <v>2.63332277796874</v>
       </c>
       <c r="F15" t="n">
-        <v>11.75278759208115</v>
+        <v>1.909827983713187</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>27.31850615954879</v>
+        <v>4.439257250926679</v>
       </c>
       <c r="D16" t="n">
-        <v>15.56781902280171</v>
+        <v>2.529770591205278</v>
       </c>
       <c r="E16" t="n">
-        <v>16.2050632490384</v>
+        <v>2.63332277796874</v>
       </c>
       <c r="F16" t="n">
-        <v>11.75278759208115</v>
+        <v>1.909827983713187</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>44.03952804997117</v>
+        <v>7.156423308120316</v>
       </c>
       <c r="D17" t="n">
-        <v>5.830951894845301</v>
+        <v>0.9475296829123614</v>
       </c>
       <c r="E17" t="n">
-        <v>16.2050632490384</v>
+        <v>2.63332277796874</v>
       </c>
       <c r="F17" t="n">
-        <v>11.75278759208115</v>
+        <v>1.909827983713187</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>71.6090845495881</v>
+        <v>11.63647623930807</v>
       </c>
       <c r="D18" t="n">
-        <v>35.30226621620771</v>
+        <v>5.736618260133753</v>
       </c>
       <c r="E18" t="n">
-        <v>16.2050632490384</v>
+        <v>2.63332277796874</v>
       </c>
       <c r="F18" t="n">
-        <v>11.75278759208115</v>
+        <v>1.909827983713187</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
